--- a/pages/WR_progressions/Women_TP.xlsx
+++ b/pages/WR_progressions/Women_TP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\WR progressions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBA5A2B-DB4F-44F2-B6AE-62B4A5FAD71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E093F77-74B4-4CC7-A3DF-03C1740917E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4118" yWindow="735" windowWidth="15000" windowHeight="12000" xr2:uid="{22AF50CD-FDEE-47EB-8810-8F22D61ED688}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{22AF50CD-FDEE-47EB-8810-8F22D61ED688}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="164" formatCode="mm:ss.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -86,12 +86,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6D3C5A8-DB7E-4260-9D28-3C08F0162801}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="9.9296875" bestFit="1" customWidth="1"/>
@@ -447,303 +445,318 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>3.2771296296296298E-3</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <f>A2*86400</f>
         <v>283.14400000000001</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>41465</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2">
         <v>41465</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>3.2420023148148147E-3</v>
       </c>
-      <c r="B3" s="3">
-        <f t="shared" ref="B3:B21" si="0">A3*86400</f>
+      <c r="B3">
+        <f t="shared" ref="B3:B22" si="0">A3*86400</f>
         <v>280.10899999999998</v>
       </c>
       <c r="C3" s="1">
         <v>41465</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>41465</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>3.2257870370370366E-3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <f t="shared" si="0"/>
         <v>278.70799999999997</v>
       </c>
       <c r="C4" s="1">
         <v>41494</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>41494</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>3.1961458333333334E-3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <f t="shared" si="0"/>
         <v>276.14699999999999</v>
       </c>
       <c r="C5" s="1">
         <v>41494</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>41494</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>3.1564930555555556E-3</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <f t="shared" si="0"/>
         <v>272.721</v>
       </c>
       <c r="C6" s="1">
         <v>41546</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>41546</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>3.1103935185185184E-3</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <f t="shared" si="0"/>
         <v>268.738</v>
       </c>
       <c r="C7" s="1">
         <v>41565</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>41565</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>3.0851388888888886E-3</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <f t="shared" si="0"/>
         <v>266.55599999999998</v>
       </c>
       <c r="C8" s="1">
         <v>41565</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>41565</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>3.0545138888888892E-3</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <f t="shared" si="0"/>
         <v>263.91000000000003</v>
       </c>
       <c r="C9" s="1">
         <v>41579</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>41579</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>3.0046759259259258E-3</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <f t="shared" si="0"/>
         <v>259.60399999999998</v>
       </c>
       <c r="C10" s="1">
         <v>41579</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>41579</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>2.9990162037037038E-3</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <f t="shared" si="0"/>
         <v>259.11500000000001</v>
       </c>
       <c r="C11" s="1">
         <v>41613</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11">
         <v>41613</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>2.9693518518518519E-3</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <f t="shared" si="0"/>
         <v>256.55200000000002</v>
       </c>
       <c r="C12" s="1">
         <v>41613</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12">
         <v>41613</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>2.9361458333333331E-3</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <f t="shared" si="0"/>
         <v>253.68299999999999</v>
       </c>
       <c r="C13" s="1">
         <v>42054</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13">
         <v>42054</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>2.9312499999999998E-3</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <f t="shared" si="0"/>
         <v>253.26</v>
       </c>
       <c r="C14" s="1">
         <v>42593</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>42593</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>2.9199305555555558E-3</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <f t="shared" si="0"/>
         <v>252.28200000000001</v>
       </c>
       <c r="C15" s="1">
         <v>42595</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15">
         <v>42595</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>2.9184259259259259E-3</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <f t="shared" si="0"/>
         <v>252.15199999999999</v>
       </c>
       <c r="C16" s="1">
         <v>42595</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16">
         <v>42595</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>2.89625E-3</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <f t="shared" si="0"/>
         <v>250.23599999999999</v>
       </c>
       <c r="C17" s="1">
         <v>42595</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17">
         <v>42595</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>2.8623495370370369E-3</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <f t="shared" si="0"/>
         <v>247.30699999999999</v>
       </c>
       <c r="C18" s="1">
         <v>44410</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18">
         <v>44410</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>2.8558796296296297E-3</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <f t="shared" si="0"/>
         <v>246.74799999999999</v>
       </c>
       <c r="C19" s="1">
         <v>44411</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19">
         <v>44411</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>2.8490625E-3</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <f t="shared" si="0"/>
         <v>246.15899999999999</v>
       </c>
       <c r="C20" s="1">
         <v>44411</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20">
         <v>44411</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>2.826875E-3</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <f t="shared" si="0"/>
         <v>244.24199999999999</v>
       </c>
       <c r="C21" s="1">
         <v>44411</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21">
         <v>44411</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
+        <v>2.8102777777777779E-3</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>242.80800000000002</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46055</v>
+      </c>
+      <c r="D22">
+        <v>46055</v>
       </c>
     </row>
   </sheetData>
